--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:12:12+00:00</t>
+    <t>2026-09-10T16:26:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:26:54+00:00</t>
+    <t>2026-09-11T08:05:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:05:56+00:00</t>
+    <t>2026-09-11T08:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:20:01+00:00</t>
+    <t>2026-09-11T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
